--- a/data/sars/atlantic/tables/Atlantic_2017_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2017_Table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8470DD4D-3C2A-9C42-A43D-C4B1F059CCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72E98D2-DA05-264C-94DF-6F3D645A5936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="840" yWindow="500" windowWidth="30740" windowHeight="21440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -409,10 +409,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="00"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -465,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -491,9 +490,6 @@
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -840,49 +836,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" x14ac:dyDescent="0.15">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="2"/>
@@ -929,10 +925,10 @@
       <c r="N2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="P2" s="14"/>
+      <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -975,10 +971,10 @@
       <c r="N3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="O3" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="P3" s="14"/>
+      <c r="P3" s="13"/>
     </row>
     <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
@@ -1021,10 +1017,10 @@
       <c r="N4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="P4" s="14"/>
+      <c r="P4" s="13"/>
     </row>
     <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
@@ -1067,8 +1063,8 @@
       <c r="N5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
@@ -1111,10 +1107,10 @@
       <c r="N6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="14" t="s">
+      <c r="O6" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="P6" s="14"/>
+      <c r="P6" s="13"/>
     </row>
     <row r="7" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
@@ -1157,8 +1153,8 @@
       <c r="N7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
     </row>
     <row r="8" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
@@ -1201,8 +1197,8 @@
       <c r="N8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
@@ -1214,13 +1210,13 @@
       <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>3785</v>
       </c>
       <c r="E9" s="3">
         <v>0.47</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>2598</v>
       </c>
       <c r="G9" s="6">
@@ -1258,13 +1254,13 @@
       <c r="C10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>3785</v>
       </c>
       <c r="E10" s="3">
         <v>0.47</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>2598</v>
       </c>
       <c r="G10" s="6">
@@ -1512,13 +1508,13 @@
       <c r="C16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <v>7092</v>
       </c>
       <c r="E16" s="6">
         <v>0.54</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <v>4632</v>
       </c>
       <c r="G16" s="6">
@@ -1554,13 +1550,13 @@
       <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <v>7092</v>
       </c>
       <c r="E17" s="6">
         <v>0.54</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <v>4632</v>
       </c>
       <c r="G17" s="6">
@@ -1596,13 +1592,13 @@
       <c r="C18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <v>7092</v>
       </c>
       <c r="E18" s="6">
         <v>0.54</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <v>4632</v>
       </c>
       <c r="G18" s="6">
@@ -1638,13 +1634,13 @@
       <c r="C19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <v>7092</v>
       </c>
       <c r="E19" s="6">
         <v>0.54</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="14">
         <v>4632</v>
       </c>
       <c r="G19" s="6">
@@ -1755,7 +1751,7 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="14" t="s">
+      <c r="O21" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1890,7 +1886,7 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="14" t="s">
+      <c r="O24" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1979,7 +1975,7 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="14" t="s">
+      <c r="O26" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2287,13 +2283,13 @@
       <c r="C34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <v>77532</v>
       </c>
       <c r="E34" s="6">
         <v>0.4</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="14">
         <v>56053</v>
       </c>
       <c r="G34" s="6">
@@ -2362,7 +2358,7 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="14" t="s">
+      <c r="O35" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2407,7 +2403,7 @@
       <c r="N36" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O36" s="14" t="s">
+      <c r="O36" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2452,7 +2448,7 @@
       <c r="N37" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O37" s="14" t="s">
+      <c r="O37" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2497,7 +2493,7 @@
       <c r="N38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="14" t="s">
+      <c r="O38" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2542,7 +2538,7 @@
       <c r="N39" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O39" s="14" t="s">
+      <c r="O39" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2587,7 +2583,7 @@
       <c r="N40" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O40" s="14" t="s">
+      <c r="O40" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2632,7 +2628,7 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="14" t="s">
+      <c r="O41" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3057,7 +3053,7 @@
       <c r="N51" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O51" s="14" t="s">
+      <c r="O51" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3104,7 +3100,7 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="14" t="s">
+      <c r="O52" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3139,7 +3135,7 @@
       <c r="J53" s="8">
         <v>5207</v>
       </c>
-      <c r="K53" s="15">
+      <c r="K53" s="14">
         <v>1088</v>
       </c>
       <c r="L53" s="3">
@@ -3151,7 +3147,7 @@
       <c r="N53" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O53" s="14" t="s">
+      <c r="O53" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3326,7 +3322,7 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="14" t="s">
+      <c r="O57" s="13" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3732,8 +3728,8 @@
       <c r="G67" s="6">
         <v>0.04</v>
       </c>
-      <c r="H67" s="9">
-        <v>4</v>
+      <c r="H67" s="5">
+        <v>0.4</v>
       </c>
       <c r="I67" s="4">
         <v>17</v>
@@ -3751,7 +3747,7 @@
       <c r="N67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O67" s="14" t="s">
+      <c r="O67" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3796,7 +3792,7 @@
       <c r="N68" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O68" s="14" t="s">
+      <c r="O68" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4349,8 +4345,8 @@
       <c r="N81" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="O81" s="13"/>
-      <c r="P81" s="13"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="12"/>
     </row>
     <row r="82" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
@@ -4395,8 +4391,8 @@
       <c r="N82" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="O82" s="13"/>
-      <c r="P82" s="13"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="12"/>
     </row>
     <row r="83" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
@@ -4439,8 +4435,8 @@
       <c r="N83" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="O83" s="14"/>
-      <c r="P83" s="14"/>
+      <c r="O83" s="13"/>
+      <c r="P83" s="13"/>
     </row>
     <row r="84" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
@@ -4485,8 +4481,8 @@
       <c r="N84" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O84" s="13"/>
-      <c r="P84" s="13"/>
+      <c r="O84" s="12"/>
+      <c r="P84" s="12"/>
     </row>
     <row r="85" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
@@ -4531,8 +4527,8 @@
       <c r="N85" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="O85" s="13"/>
-      <c r="P85" s="13"/>
+      <c r="O85" s="12"/>
+      <c r="P85" s="12"/>
     </row>
     <row r="86" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
@@ -4575,8 +4571,8 @@
       <c r="N86" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="O86" s="13"/>
-      <c r="P86" s="13"/>
+      <c r="O86" s="12"/>
+      <c r="P86" s="12"/>
     </row>
     <row r="87" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A87" s="3" t="s">
@@ -4619,8 +4615,8 @@
       <c r="N87" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O87" s="13"/>
-      <c r="P87" s="13"/>
+      <c r="O87" s="12"/>
+      <c r="P87" s="12"/>
     </row>
     <row r="88" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A88" s="3" t="s">
@@ -4663,8 +4659,8 @@
       <c r="N88" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O88" s="13"/>
-      <c r="P88" s="13"/>
+      <c r="O88" s="12"/>
+      <c r="P88" s="12"/>
     </row>
     <row r="89" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A89" s="3" t="s">
@@ -4707,8 +4703,8 @@
       <c r="N89" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O89" s="13"/>
-      <c r="P89" s="13"/>
+      <c r="O89" s="12"/>
+      <c r="P89" s="12"/>
     </row>
     <row r="90" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A90" s="3" t="s">
@@ -4751,8 +4747,8 @@
       <c r="N90" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O90" s="13"/>
-      <c r="P90" s="13"/>
+      <c r="O90" s="12"/>
+      <c r="P90" s="12"/>
     </row>
     <row r="91" spans="1:16" ht="15" x14ac:dyDescent="0.15">
       <c r="A91" s="3" t="s">
@@ -4795,8 +4791,8 @@
       <c r="N91" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="O91" s="13"/>
-      <c r="P91" s="13"/>
+      <c r="O91" s="12"/>
+      <c r="P91" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
